--- a/AAII_Financials/Yearly/MRT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MRT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>MRT</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -696,8 +696,8 @@
       <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
+      <c r="I7" s="2">
+        <v>44196</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
@@ -726,8 +726,8 @@
       <c r="H8" s="3">
         <v>17000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
+      <c r="I8" s="3">
+        <v>9800</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -756,8 +756,8 @@
       <c r="H9" s="3">
         <v>16400</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+      <c r="I9" s="3">
+        <v>9000</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -786,8 +786,8 @@
       <c r="H10" s="3">
         <v>600</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+      <c r="I10" s="3">
+        <v>800</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -830,8 +830,8 @@
       <c r="H12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
+      <c r="I12" s="3">
+        <v>500</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -890,8 +890,8 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -921,7 +921,7 @@
         <v>5500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -961,8 +961,8 @@
       <c r="H17" s="3">
         <v>26000</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
+      <c r="I17" s="3">
+        <v>13800</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -991,8 +991,8 @@
       <c r="H18" s="3">
         <v>-9000</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
+      <c r="I18" s="3">
+        <v>-4000</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1035,8 +1035,8 @@
       <c r="H20" s="3">
         <v>4100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>400</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1066,7 +1066,7 @@
         <v>-7600</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -1095,8 +1095,8 @@
       <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>200</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1125,8 +1125,8 @@
       <c r="H23" s="3">
         <v>-13600</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
+      <c r="I23" s="3">
+        <v>-4600</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1215,8 +1215,8 @@
       <c r="H26" s="3">
         <v>-14500</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
+      <c r="I26" s="3">
+        <v>-4600</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1245,8 +1245,8 @@
       <c r="H27" s="3">
         <v>-14500</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
+      <c r="I27" s="3">
+        <v>-4600</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1395,8 +1395,8 @@
       <c r="H32" s="3">
         <v>-4100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>-400</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1425,8 +1425,8 @@
       <c r="H33" s="3">
         <v>-14500</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
+      <c r="I33" s="3">
+        <v>-4600</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1485,8 +1485,8 @@
       <c r="H35" s="3">
         <v>-14500</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
+      <c r="I35" s="3">
+        <v>-4600</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1520,8 +1520,8 @@
       <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
+      <c r="I38" s="2">
+        <v>44196</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
@@ -1575,11 +1575,11 @@
       <c r="G41" s="3">
         <v>10500</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
+      <c r="H41" s="3">
+        <v>13200</v>
+      </c>
+      <c r="I41" s="3">
+        <v>3500</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1635,11 +1635,11 @@
       <c r="G43" s="3">
         <v>3400</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I43" s="3">
+        <v>900</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1665,11 +1665,11 @@
       <c r="G44" s="3">
         <v>3300</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
+      <c r="H44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I44" s="3">
+        <v>300</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -1695,11 +1695,11 @@
       <c r="G45" s="3">
         <v>3200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>800</v>
+      </c>
+      <c r="I45" s="3">
+        <v>500</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1725,11 +1725,11 @@
       <c r="G46" s="3">
         <v>20500</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
+      <c r="H46" s="3">
+        <v>18000</v>
+      </c>
+      <c r="I46" s="3">
+        <v>5600</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -1785,11 +1785,11 @@
       <c r="G48" s="3">
         <v>20200</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
+      <c r="H48" s="3">
+        <v>14200</v>
+      </c>
+      <c r="I48" s="3">
+        <v>4100</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -1818,8 +1818,8 @@
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -1905,11 +1905,11 @@
       <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3900</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -1965,11 +1965,11 @@
       <c r="G54" s="3">
         <v>40900</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
+      <c r="H54" s="3">
+        <v>39000</v>
+      </c>
+      <c r="I54" s="3">
+        <v>13600</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2023,11 +2023,11 @@
       <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
+      <c r="H57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>800</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2054,10 +2054,10 @@
         <v>9400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+        <v>6300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>9000</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2083,11 +2083,11 @@
       <c r="G59" s="3">
         <v>1700</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
+      <c r="H59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>100</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2113,11 +2113,11 @@
       <c r="G60" s="3">
         <v>15900</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
+      <c r="H60" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I60" s="3">
+        <v>10500</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2144,10 +2144,10 @@
         <v>17100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2173,11 +2173,11 @@
       <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2293,11 +2293,11 @@
       <c r="G66" s="3">
         <v>33300</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
+      <c r="H66" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I66" s="3">
+        <v>11000</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2398,10 +2398,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>51300</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -2457,11 +2457,11 @@
       <c r="G72" s="3">
         <v>-39200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
+      <c r="H72" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-10500</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2577,11 +2577,11 @@
       <c r="G76" s="3">
         <v>7600</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
+      <c r="H76" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="I76" s="3">
+        <v>-10000</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2645,8 +2645,8 @@
       <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
+      <c r="I80" s="2">
+        <v>44196</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
@@ -2675,8 +2675,8 @@
       <c r="H81" s="3">
         <v>-14500</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
+      <c r="I81" s="3">
+        <v>-4600</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -2719,8 +2719,8 @@
       <c r="H83" s="3">
         <v>5500</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>2700</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -2899,8 +2899,8 @@
       <c r="H89" s="3">
         <v>-4000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+      <c r="I89" s="3">
+        <v>-1100</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -2943,8 +2943,8 @@
       <c r="H91" s="3">
         <v>-22800</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
+      <c r="I91" s="3">
+        <v>-9200</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -3033,8 +3033,8 @@
       <c r="H94" s="3">
         <v>-22900</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+      <c r="I94" s="3">
+        <v>-9200</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -3197,8 +3197,8 @@
       <c r="H100" s="3">
         <v>43100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+      <c r="I100" s="3">
+        <v>10400</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
@@ -3227,8 +3227,8 @@
       <c r="H101" s="3">
         <v>-6500</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>-200</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -3258,7 +3258,7 @@
         <v>9700</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
